--- a/src/utils/sxsyzlzq/shijiesai/all_count.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/all_count.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395"/>
+    <workbookView windowWidth="17625" windowHeight="10680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,16 +73,16 @@
     <t>144-zwy(九霄环佩)</t>
   </si>
   <si>
+    <t>149-灰企鹅呆瓜</t>
+  </si>
+  <si>
+    <t>146-江南</t>
+  </si>
+  <si>
+    <t>145-掌管贫穷的神(Mr.Go)</t>
+  </si>
+  <si>
     <t>156-Tiao跳猪</t>
-  </si>
-  <si>
-    <t>149-灰企鹅呆瓜</t>
-  </si>
-  <si>
-    <t>146-江南</t>
-  </si>
-  <si>
-    <t>145-掌管贫穷的神(Mr.Go)</t>
   </si>
   <si>
     <t>137-鹰の一手</t>
@@ -1320,9 +1320,6 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="G7">
         <v>1</v>
       </c>
@@ -1331,7 +1328,7 @@
       </c>
       <c r="I7">
         <f>SUM(B7:H7)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1341,11 +1338,8 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
       <c r="H8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <f>SUM(B8:H8)</f>
@@ -1356,15 +1350,18 @@
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="H9">
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
       <c r="I9">
         <f>SUM(B9:H9)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1378,7 +1375,10 @@
         <v>1</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
       </c>
       <c r="I10">
         <f>SUM(B10:H10)</f>
@@ -2155,7 +2155,7 @@
     </row>
   </sheetData>
   <sortState ref="A2:I70">
-    <sortCondition ref="B2" descending="1"/>
+    <sortCondition ref="B3" descending="1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/src/utils/sxsyzlzq/shijiesai/all_count.xlsx
+++ b/src/utils/sxsyzlzq/shijiesai/all_count.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1404,7 +1404,7 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <f>SUM(B2:H2)</f>
+        <f t="shared" ref="I2:I65" si="0">SUM(B2:H2)</f>
         <v>9</v>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <f>SUM(B3:H3)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <f>SUM(B4:H4)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <f>SUM(B5:H5)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <f>SUM(B6:H6)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <f>SUM(B7:H7)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
         <v>2</v>
       </c>
       <c r="I8">
-        <f>SUM(B8:H8)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>2</v>
       </c>
       <c r="I9">
-        <f>SUM(B9:H9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <f>SUM(B10:H10)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
         <v>3</v>
       </c>
       <c r="I11">
-        <f>SUM(B11:H11)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
         <v>2</v>
       </c>
       <c r="I12">
-        <f>SUM(B12:H12)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <f>SUM(B13:H13)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="I14">
-        <f>SUM(B14:H14)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <f>SUM(B15:H15)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
         <v>2</v>
       </c>
       <c r="I16">
-        <f>SUM(B16:H16)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
         <v>2</v>
       </c>
       <c r="I17">
-        <f>SUM(B17:H17)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
         <v>2</v>
       </c>
       <c r="I18">
-        <f>SUM(B18:H18)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
         <v>4</v>
       </c>
       <c r="I19">
-        <f>SUM(B19:H19)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="I20">
-        <f>SUM(B20:H20)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
         <v>3</v>
       </c>
       <c r="I21">
-        <f>SUM(B21:H21)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
         <v>2</v>
       </c>
       <c r="I22">
-        <f>SUM(B22:H22)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
         <v>4</v>
       </c>
       <c r="I23">
-        <f>SUM(B23:H23)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="I24">
-        <f>SUM(B24:H24)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <f>SUM(B25:H25)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
         <v>2</v>
       </c>
       <c r="I26">
-        <f>SUM(B26:H26)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <f>SUM(B27:H27)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
         <v>3</v>
       </c>
       <c r="I28">
-        <f>SUM(B28:H28)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
         <v>2</v>
       </c>
       <c r="I29">
-        <f>SUM(B29:H29)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
         <v>4</v>
       </c>
       <c r="I30">
-        <f>SUM(B30:H30)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
         <v>3</v>
       </c>
       <c r="I31">
-        <f>SUM(B31:H31)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
         <v>2</v>
       </c>
       <c r="I32">
-        <f>SUM(B32:H32)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
         <v>2</v>
       </c>
       <c r="I33">
-        <f>SUM(B33:H33)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         <v>2</v>
       </c>
       <c r="I34">
-        <f>SUM(B34:H34)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
         <v>6</v>
       </c>
       <c r="I35">
-        <f>SUM(B35:H35)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
         <v>3</v>
       </c>
       <c r="I36">
-        <f>SUM(B36:H36)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="I37">
-        <f>SUM(B37:H37)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
         <v>2</v>
       </c>
       <c r="I38">
-        <f>SUM(B38:H38)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2037,7 +2037,7 @@
         <v>2</v>
       </c>
       <c r="I39">
-        <f>SUM(B39:H39)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <f>SUM(B40:H40)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2063,9 +2063,8 @@
       <c r="G41">
         <v>1</v>
       </c>
-      <c r="H41"/>
       <c r="I41">
-        <f>SUM(B41:H41)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2077,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <f>SUM(B42:H42)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2089,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <f>SUM(B43:H43)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2101,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <f>SUM(B44:H44)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2113,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <f>SUM(B45:H45)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2125,7 +2124,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <f>SUM(B46:H46)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2137,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <f>SUM(B47:H47)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2149,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <f>SUM(B48:H48)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -2161,7 +2160,7 @@
         <v>6</v>
       </c>
       <c r="I49">
-        <f>SUM(B49:H49)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -2173,7 +2172,7 @@
         <v>4</v>
       </c>
       <c r="I50">
-        <f>SUM(B50:H50)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -2185,7 +2184,7 @@
         <v>4</v>
       </c>
       <c r="I51">
-        <f>SUM(B51:H51)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
@@ -2197,7 +2196,7 @@
         <v>3</v>
       </c>
       <c r="I52">
-        <f>SUM(B52:H52)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2209,7 +2208,7 @@
         <v>3</v>
       </c>
       <c r="I53">
-        <f>SUM(B53:H53)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -2221,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <f>SUM(B54:H54)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2233,7 +2232,7 @@
         <v>2</v>
       </c>
       <c r="I55">
-        <f>SUM(B55:H55)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2245,7 +2244,7 @@
         <v>2</v>
       </c>
       <c r="I56">
-        <f>SUM(B56:H56)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2257,7 +2256,7 @@
         <v>2</v>
       </c>
       <c r="I57">
-        <f>SUM(B57:H57)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2269,7 +2268,7 @@
         <v>2</v>
       </c>
       <c r="I58">
-        <f>SUM(B58:H58)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2281,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="I59">
-        <f>SUM(B59:H59)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2293,7 +2292,7 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <f>SUM(B60:H60)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2305,7 +2304,7 @@
         <v>2</v>
       </c>
       <c r="I61">
-        <f>SUM(B61:H61)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2317,7 +2316,7 @@
         <v>2</v>
       </c>
       <c r="I62">
-        <f>SUM(B62:H62)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2329,7 +2328,7 @@
         <v>2</v>
       </c>
       <c r="I63">
-        <f>SUM(B63:H63)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2341,7 +2340,7 @@
         <v>2</v>
       </c>
       <c r="I64">
-        <f>SUM(B64:H64)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2353,7 +2352,7 @@
         <v>2</v>
       </c>
       <c r="I65">
-        <f>SUM(B65:H65)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -2365,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <f>SUM(B66:H66)</f>
+        <f t="shared" ref="I66:I97" si="1">SUM(B66:H66)</f>
         <v>1</v>
       </c>
     </row>
@@ -2377,7 +2376,7 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <f>SUM(B67:H67)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2389,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="I68">
-        <f>SUM(B68:H68)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2401,7 +2400,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <f>SUM(B69:H69)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2413,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <f>SUM(B70:H70)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2425,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <f>SUM(B71:H71)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2437,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <f>SUM(B72:H72)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2449,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <f>SUM(B73:H73)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2461,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <f>SUM(B74:H74)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2473,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <f>SUM(B75:H75)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2485,7 +2484,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <f>SUM(B76:H76)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2497,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <f>SUM(B77:H77)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2509,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <f>SUM(B78:H78)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2521,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <f>SUM(B79:H79)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2533,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <f>SUM(B80:H80)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2545,7 +2544,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <f>SUM(B81:H81)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2557,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <f>SUM(B82:H82)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2569,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <f>SUM(B83:H83)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2581,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <f>SUM(B84:H84)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2593,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <f>SUM(B85:H85)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2605,7 +2604,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <f>SUM(B86:H86)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2617,7 +2616,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <f>SUM(B87:H87)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2629,7 +2628,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <f>SUM(B88:H88)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2641,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="I89">
-        <f>SUM(B89:H89)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2653,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <f>SUM(B90:H90)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2665,7 +2664,7 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <f>SUM(B91:H91)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2677,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <f>SUM(B92:H92)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2689,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <f>SUM(B93:H93)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2701,7 +2700,7 @@
         <v>1</v>
       </c>
       <c r="I94">
-        <f>SUM(B94:H94)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2713,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <f>SUM(B95:H95)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2725,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <f>SUM(B96:H96)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2737,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <f>SUM(B97:H97)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -2746,39 +2745,39 @@
         <v>105</v>
       </c>
       <c r="B100">
-        <f t="shared" ref="B100:I100" si="0">SUM(B2:B97)</f>
+        <f t="shared" ref="B100:I100" si="2">SUM(B2:B97)</f>
         <v>9</v>
       </c>
       <c r="C100">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="D100">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="E100">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="F100">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="G100">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="H100">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="I100">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>288</v>
       </c>
     </row>
-    <row r="103" spans="2:5">
+    <row r="103" spans="1:9">
       <c r="B103" s="1" t="s">
         <v>1</v>
       </c>
@@ -2792,7 +2791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:9">
       <c r="A104" s="1" t="s">
         <v>106</v>
       </c>
@@ -2809,7 +2808,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:9">
       <c r="A105" s="1" t="s">
         <v>111</v>
       </c>
@@ -2826,7 +2825,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:9">
       <c r="A106" s="1" t="s">
         <v>114</v>
       </c>
@@ -2843,7 +2842,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:9">
       <c r="A107" s="1" t="s">
         <v>116</v>
       </c>
@@ -2860,7 +2859,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:9">
       <c r="A108" s="1" t="s">
         <v>119</v>
       </c>
@@ -2877,7 +2876,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:9">
       <c r="A109" s="1" t="s">
         <v>121</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:9">
       <c r="A110" s="1" t="s">
         <v>124</v>
       </c>
@@ -2911,7 +2910,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:9">
       <c r="A111" s="1" t="s">
         <v>126</v>
       </c>
@@ -2928,7 +2927,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:9">
       <c r="A112" s="1" t="s">
         <v>128</v>
       </c>
